--- a/output/pdf_financials_xlsx/GEI.xlsx
+++ b/output/pdf_financials_xlsx/GEI.xlsx
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.471</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.832</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1698,13 +1698,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>140.721</v>
+        <v>141.192</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>127.529</v>
+        <v>128.361</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-287.344</v>
+        <v>-286.786</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-234.617</v>
@@ -1794,13 +1794,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>190.924</v>
+        <v>191.395</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>182.52</v>
+        <v>183.352</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-199.79</v>
+        <v>-199.232</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-234.617</v>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2.750801111535502</v>
+        <v>2.757587200887984</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2.128878318368084</v>
+        <v>2.138582606998822</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-3.572794046905015</v>
+        <v>-3.562815474012613</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-5.106829704793955</v>
@@ -6569,25 +6569,25 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-49.792</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-48.632</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-36.694</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-35.397</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-35.896</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-350</v>
+        <v>-380.241</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>-325</v>
+        <v>-350.618</v>
       </c>
     </row>
     <row r="125">
@@ -6617,25 +6617,25 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-49.792</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-48.632</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-36.694</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-35.397</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-35.896</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-350</v>
+        <v>-380.241</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-325</v>
+        <v>-350.618</v>
       </c>
     </row>
     <row r="126">
@@ -26675,7 +26675,11 @@
           <t>Lease payments 14</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -28085,7 +28089,11 @@
           <t>Lease payments 15</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -31105,7 +31113,11 @@
           <t>Finance lease payments (note 15)......................................................................................</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -33416,7 +33428,11 @@
           <t>Finance lease payments (note 16)......................................................................................</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -47770,7 +47786,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -47847,7 +47863,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -48471,7 +48487,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">

--- a/output/pdf_financials_xlsx/GEI.xlsx
+++ b/output/pdf_financials_xlsx/GEI.xlsx
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>50.203</v>
+        <v>184.057</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>54.991</v>
+        <v>209.925</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>87.554</v>
+        <v>282.992</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>191.395</v>
+        <v>325.249</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>183.352</v>
+        <v>338.286</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-199.232</v>
+        <v>-3.794</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-234.617</v>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2.757587200887984</v>
+        <v>4.686133281964606</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2.138582606998822</v>
+        <v>3.945703105454009</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-3.562815474012613</v>
+        <v>-0.0678471425694861</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-5.106829704793955</v>
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>184.057</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>209.925</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>282.992</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -28411,7 +28411,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -28893,7 +28897,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs 18</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -36247,7 +36255,11 @@
           <t>Depreciation of property, plant and equipment (notes 9 and 21) .......................................</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -36328,7 +36340,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -39103,7 +39115,11 @@
           <t>Depreciation of property, plant and equipment (note 21) ...................................................</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -39184,7 +39200,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
